--- a/Data Model.xlsx
+++ b/Data Model.xlsx
@@ -34,10 +34,10 @@
     <t>INT</t>
   </si>
   <si>
-    <t>PRIMARY KEY, AUTO_INCREMENT</t>
-  </si>
-  <si>
-    <t>Mã tài khoản tự tăng</t>
+    <t>PRIMARY KEY</t>
+  </si>
+  <si>
+    <t>Unique account identifier</t>
   </si>
   <si>
     <t>username</t>
@@ -49,7 +49,7 @@
     <t>NOT NULL, UNIQUE</t>
   </si>
   <si>
-    <t>Tên đăng nhập</t>
+    <t>Login username</t>
   </si>
   <si>
     <t>password</t>
@@ -61,7 +61,7 @@
     <t>NOT NULL</t>
   </si>
   <si>
-    <t>Mật khẩu (đã mã hóa)</t>
+    <t>Account password</t>
   </si>
   <si>
     <t>fullname</t>
@@ -70,7 +70,7 @@
     <t>VARCHAR(100)</t>
   </si>
   <si>
-    <t>Họ và tên người dùng</t>
+    <t>User's full name</t>
   </si>
   <si>
     <t>email</t>
@@ -79,25 +79,28 @@
     <t>NULL</t>
   </si>
   <si>
-    <t>Địa chỉ Email</t>
+    <t>User's email</t>
   </si>
   <si>
     <t>phone</t>
   </si>
   <si>
+    <t>VARCHAR(15)</t>
+  </si>
+  <si>
+    <t>User's phone number</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
     <t>VARCHAR(20)</t>
   </si>
   <si>
-    <t>Số điện thoại tài khoản</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>NOT NULL (Default: 'User')</t>
-  </si>
-  <si>
-    <t>Phân quyền ('User' hoặc 'Admin')</t>
+    <t xml:space="preserve">NOT NULL </t>
+  </si>
+  <si>
+    <t>Account role: User/Admin</t>
   </si>
   <si>
     <t>Bảng Groups</t>
@@ -106,25 +109,25 @@
     <t>group_id</t>
   </si>
   <si>
-    <t>Mã nhóm tự tăng</t>
+    <t>Unique group identifier</t>
   </si>
   <si>
     <t>group_name</t>
   </si>
   <si>
-    <t>Tên nhóm (Công việc, Gia đình,…)</t>
+    <t>Group name</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
-    <t>Mô tả chi tiết về nhóm</t>
+    <t>Group description</t>
   </si>
   <si>
     <t>FOREIGN KEY REFERENCES accounts(account_id)</t>
   </si>
   <si>
-    <t>Mã tài khoản sở hữu nhóm</t>
+    <t>Owner account</t>
   </si>
   <si>
     <t>Bảng Contacts</t>
@@ -133,25 +136,25 @@
     <t>contact_id</t>
   </si>
   <si>
-    <t>Mã liên hệ tự tăng</t>
+    <t>Unique contact identifier</t>
   </si>
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>Họ và tên liên hệ</t>
-  </si>
-  <si>
-    <t>Số điện thoại liên hệ</t>
-  </si>
-  <si>
-    <t>Email liên hệ</t>
+    <t>Contact name</t>
+  </si>
+  <si>
+    <t>Contact phone number</t>
+  </si>
+  <si>
+    <t>Contact email</t>
   </si>
   <si>
     <t>address</t>
   </si>
   <si>
-    <t>Địa chỉ liên hệ</t>
+    <t>Contact address</t>
   </si>
   <si>
     <t>is_favorite</t>
@@ -163,16 +166,13 @@
     <t>NOT NULL (Default: FALSE)</t>
   </si>
   <si>
-    <t>Trạng thái yêu thích ( true/false)</t>
-  </si>
-  <si>
-    <t>Mã tài khoản sở hữu</t>
+    <t>Favorite status</t>
   </si>
   <si>
     <t>FOREIGN KEY REFERENCES groups(group_id)</t>
   </si>
   <si>
-    <t>Mã nhóm phân loại (Có thể NULL)</t>
+    <t>Contact's group</t>
   </si>
 </sst>
 </file>
@@ -778,18 +778,18 @@
         <v>26</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -811,7 +811,7 @@
     </row>
     <row r="14" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>6</v>
@@ -820,12 +820,12 @@
         <v>7</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>18</v>
@@ -834,21 +834,21 @@
         <v>15</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -859,10 +859,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -885,7 +885,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -907,7 +907,7 @@
     </row>
     <row r="23" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>6</v>
@@ -916,12 +916,12 @@
         <v>7</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>18</v>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -944,7 +944,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -958,12 +958,12 @@
         <v>21</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>14</v>
@@ -972,21 +972,21 @@
         <v>21</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -997,15 +997,15 @@
         <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>6</v>

--- a/Data Model.xlsx
+++ b/Data Model.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
   <si>
     <t>Bảng Accounts</t>
   </si>
@@ -58,63 +58,63 @@
     <t>VARCHAR(255)</t>
   </si>
   <si>
+    <t>Account password</t>
+  </si>
+  <si>
+    <t>fullname</t>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+  </si>
+  <si>
+    <t>User's full name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>User's email</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>VARCHAR(15)</t>
+  </si>
+  <si>
+    <t>User's phone number</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>VARCHAR(20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT NULL </t>
+  </si>
+  <si>
+    <t>Account role: User/Admin</t>
+  </si>
+  <si>
+    <t>Bảng Groups</t>
+  </si>
+  <si>
+    <t>group_id</t>
+  </si>
+  <si>
+    <t>Unique group identifier</t>
+  </si>
+  <si>
+    <t>group_name</t>
+  </si>
+  <si>
     <t>NOT NULL</t>
   </si>
   <si>
-    <t>Account password</t>
-  </si>
-  <si>
-    <t>fullname</t>
-  </si>
-  <si>
-    <t>VARCHAR(100)</t>
-  </si>
-  <si>
-    <t>User's full name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t>User's email</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>VARCHAR(15)</t>
-  </si>
-  <si>
-    <t>User's phone number</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>VARCHAR(20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT NULL </t>
-  </si>
-  <si>
-    <t>Account role: User/Admin</t>
-  </si>
-  <si>
-    <t>Bảng Groups</t>
-  </si>
-  <si>
-    <t>group_id</t>
-  </si>
-  <si>
-    <t>Unique group identifier</t>
-  </si>
-  <si>
-    <t>group_name</t>
-  </si>
-  <si>
     <t>Group name</t>
   </si>
   <si>
@@ -169,17 +169,20 @@
     <t>Favorite status</t>
   </si>
   <si>
-    <t>FOREIGN KEY REFERENCES groups(group_id)</t>
-  </si>
-  <si>
-    <t>Contact's group</t>
+    <t>Contacts_Groups</t>
+  </si>
+  <si>
+    <t>PRIMARY KEY, FOREIGN KEY REFERENCES Contacts(contact_id)</t>
+  </si>
+  <si>
+    <t>PRIMARY KEY, FOREIGN KEY REFERENCES Groups(group_id)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -204,6 +207,11 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -277,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -316,6 +324,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -657,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21.285714285714285" customWidth="1"/>
@@ -667,7 +684,7 @@
     <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -689,7 +706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="42.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -703,7 +720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="42.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -717,7 +734,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="42.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -725,71 +742,71 @@
         <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4" t="s">
+    </row>
+    <row r="6" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" ht="42.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="4" t="s">
+    </row>
+    <row r="7" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" ht="42.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="4" t="s">
+    </row>
+    <row r="8" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" ht="42.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="4" t="s">
+    </row>
+    <row r="9" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" ht="42.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4" t="s">
+    </row>
+    <row r="12" ht="12.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -809,9 +826,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>6</v>
@@ -820,24 +837,24 @@
         <v>7</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>35</v>
       </c>
@@ -845,13 +862,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>5</v>
       </c>
@@ -883,7 +900,7 @@
       <c r="C20" s="13"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" ht="12.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
@@ -892,20 +909,20 @@
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -919,49 +936,49 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="C25" s="5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>46</v>
       </c>
@@ -969,13 +986,13 @@
         <v>14</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>48</v>
       </c>
@@ -989,7 +1006,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1003,25 +1020,98 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" ht="36.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+    <row r="30" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="12"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" ht="52.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" ht="52.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>53</v>
-      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="11"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="12"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="11"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="11"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="11"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Data Model.xlsx
+++ b/Data Model.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CCDF484-0B06-4384-B39B-2C83D2C7F097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="56">
   <si>
     <t>Bảng Accounts</t>
   </si>
@@ -46,7 +50,7 @@
     <t>VARCHAR(50)</t>
   </si>
   <si>
-    <t>NOT NULL, UNIQUE</t>
+    <t>NOT NULL</t>
   </si>
   <si>
     <t>Login username</t>
@@ -94,7 +98,7 @@
     <t>VARCHAR(20)</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT NULL </t>
+    <t>NOT NULL, DEFAULT 'user'</t>
   </si>
   <si>
     <t>Account role: User/Admin</t>
@@ -112,9 +116,6 @@
     <t>group_name</t>
   </si>
   <si>
-    <t>NOT NULL</t>
-  </si>
-  <si>
     <t>Group name</t>
   </si>
   <si>
@@ -124,9 +125,6 @@
     <t>Group description</t>
   </si>
   <si>
-    <t>FOREIGN KEY REFERENCES accounts(account_id)</t>
-  </si>
-  <si>
     <t>Owner account</t>
   </si>
   <si>
@@ -169,6 +167,9 @@
     <t>Favorite status</t>
   </si>
   <si>
+    <t>NOT NULL, FOREIGN KEY REFERENCES Accounts(account_id)</t>
+  </si>
+  <si>
     <t>Contacts_Groups</t>
   </si>
   <si>
@@ -176,29 +177,37 @@
   </si>
   <si>
     <t>PRIMARY KEY, FOREIGN KEY REFERENCES Groups(group_id)</t>
+  </si>
+  <si>
+    <t>Group reference</t>
+  </si>
+  <si>
+    <t>Contact reference</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -207,11 +216,13 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -287,53 +298,53 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -673,438 +684,438 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.285714285714285" customWidth="1"/>
-    <col min="2" max="2" width="21.428571428571427" customWidth="1"/>
-    <col min="3" max="3" width="32.42857142857143" customWidth="1"/>
-    <col min="4" max="4" width="26.571428571428573" customWidth="1"/>
-    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" customWidth="1"/>
+    <col min="5" max="24" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="12.6" customHeight="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" ht="34.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" ht="12.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:4" ht="10.199999999999999" customHeight="1">
+      <c r="A12" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:4" ht="21" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:4" ht="21" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="4" t="s">
+    </row>
+    <row r="16" spans="1:4" ht="21" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="4" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="48" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="11"/>
+    </row>
+    <row r="21" spans="1:4" ht="10.199999999999999" customHeight="1">
+      <c r="A21" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="23.4" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="23.4" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="23.4" customHeight="1">
+      <c r="A25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="23.4" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="23.4" customHeight="1">
+      <c r="A27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D27" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="23.4" customHeight="1">
+      <c r="A28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="46.8" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="7" t="s">
+    <row r="30" spans="1:4" ht="23.4" customHeight="1">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="11"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="42" customHeight="1">
+      <c r="A35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="12"/>
-    </row>
-    <row r="21" ht="12.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="C35" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="42" customHeight="1">
+      <c r="A36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="12"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" ht="52.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="16" t="s">
+      <c r="C36" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" ht="52.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="D36" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="11"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="12"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="11"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="11"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="12"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="11"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="12"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="11"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="11"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1114,6 +1125,6 @@
     <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>